--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0250AE8-BDE8-4DB3-8393-85F3CEB5C17A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{350D740B-1293-4747-83F3-9531E159CA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="52">
   <si>
     <t>s</t>
   </si>
@@ -74,198 +74,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>全额拨款</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>财政补助 （财政拨款）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>财政补助</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ABA98B9BC286D6957C4A29991736A24A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>苏州杂志社</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12320500466954885X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>弘扬吴文化，服务精神文明建设。 出版《苏州杂志》双月期刊。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>苏州市滚绣坊青石弄5号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>朱红梅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>38.83万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>苏州市文学艺术界联合会</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2025年02月24日 至 2030年02月24日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>B608A612038807B0181B1B4C50A2D9F2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>广西科技大学</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>124500004985963814</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>培养高等学历人才，开展硕士研究生和本专科学历教育，并进行相关科学研究、继续教育、专业培训、学术交流和相关社会服务，以促进科技发展和社会进步。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>柳州市文昌路2号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刘宝臣</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>94505.9万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>广西壮族自治区教育厅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2025年03月18日 至 2030年03月17日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>121500004600222007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>88446CF827EA575A10369E0A80DBF808</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>内蒙古电子信息职业技术学院</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>坚持把铸牢中华民族共同体意识作为教育工作的主线 贯穿于办学治校 教书育人 科学研究 人才培养 服务社会等全过程各方面 培养大专学历和本科学历人才 从事电子信息学科 高等职业教育 大专教育 本科教育 中专教育和学科继续教育</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>内蒙古呼和浩特市赛罕区苏尔干街8号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>林民</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>103517万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>内蒙古自治区教育厅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2022年03月24日 至 2027年03月24日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0CC57AED37C296D822B0DA1F4760B044</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>连云港市体育训练中心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12320700MB0598663C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>促进田径，皮、划、赛艇，自行车，拳击运动发展。后备人才培养与输送。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>江苏省连云港市科教创业园区霞晖路99号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>徐庚勇</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>141万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>连云港市体育局</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2024年12月10日 至 2029年12月10日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>E07B841B0DF4BBB01F601E595A5FC840</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>内蒙古机电职业技术学院</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12150000460027503M</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>坚持把铸牢中华民族共同体意识作为教育工作的主线 贯穿于办学治校 教书育人 科学研究 人才培养 服务社会等全过程各方面 面向行业 服务全区 以高等职业教育为主体 兼办中等职业教育和成人继续教育，开展科学研究、技术服务、培训、技术转移及成果转化等业务。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>呼和浩特市赛罕区学府路1号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>赵卫国</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>财政补助 （全额拨款）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>40226万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2023年03月23日 至 2028年03月23日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>天长市社会福利院</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -379,6 +191,46 @@
   </si>
   <si>
     <t>自 2022年02月24日 至 2027年02月23日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>滨州市市政公用发展服务中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12371600MB23431700</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A1DBA9E5588D9EE45BBE4B3F682FC962</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>贯彻党中央、省关于城镇燃气、城市集中供热、市政设施管理等方面的方针政策和决策部署，落实市委、市政府工作要求。协助做好城镇燃气城市集中供热管理、村镇建设管理、市政公用设施管理、市政公用行业应急管理、市政公用设施养护维修管理、市政公用设施巡查管理等相关工作。负责辖区职责范围内城镇燃气、城市集中供热、市政设施管理等方面工作。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>滨州市黄河五路355号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>徐波</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>待定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6133.19万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>滨州市住房和城乡建设局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2026年07月03日 至 2031年03月31日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -764,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -820,31 +672,31 @@
         <v>15</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>20</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>11</v>
@@ -852,25 +704,25 @@
     </row>
     <row r="3" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>14</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>30</v>
@@ -890,22 +742,22 @@
         <v>34</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>33</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>13</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>39</v>
@@ -922,13 +774,13 @@
     </row>
     <row r="5" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>45</v>
@@ -940,158 +792,18 @@
         <v>47</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="K9" s="1" t="s">
         <v>11</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{350D740B-1293-4747-83F3-9531E159CA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4130B519-34FD-4BFF-8ED2-0333BDCCA389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
   <si>
     <t>s</t>
   </si>
@@ -74,90 +74,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>财政补助 （财政拨款）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>天长市社会福利院</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12341181F14339784T</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0189DF92EDC0B0177A49C44938D21167</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>提供收养服务，弘扬救助精神。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>天长市冶山镇塔山村</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>吴万兵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11.55万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>天长市民政局</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2025年02月21日 至 2030年02月20日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>龙川县福利院</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>封开县福利院</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>12441622456981927F</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2F25E9B3DF30F77560E8E29C583EEB76</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>承担社会公益性职能，提供收养服务，弘扬救助精神；全心全意为供养、代养人员建立平等、团结、友爱互助的社会主义人际关系，负责收养社会三无老人、残疾老人社会福利事务。负责收养入住的全县孤老重点优抚对象的生活、医疗、管理与服务工作；负责城镇三无老人的收养；提供老人自愿有偿代养服务。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>广东省龙川县义都镇星光村</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>陈智宏</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>财政补助 （财政补助二类）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>156万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>龙川县民政局</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2026年06月16日 至 2031年06月15日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>12441225070255594J</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -231,6 +151,46 @@
   </si>
   <si>
     <t>自 2026年07月03日 至 2031年03月31日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>郑州大学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12410000415800376M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>97E96F7AAB8A38F2E5C26B67DA17A964</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>培养高等学历人才，促进科技文化发展。　哲学类、经济学类、法学类、教育学类、文学类、历史学类、理学类、工学类、农学类、医学类、管理学类大学专科、本科、研究生班、硕士研究生、博士研究生学历教育　博士后培养　相关科学研究、继续教育、专业培训与学术交流　相关社会服务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河南省郑州市高新技术开发区科学大道100号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李蓬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政补助 （财政补助收入、事业收入、其它收入）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>939805万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河南省教育厅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2022年06月22日 至 2027年06月22日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -616,7 +576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -669,25 +629,25 @@
     </row>
     <row r="2" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>12</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>19</v>
@@ -704,34 +664,34 @@
     </row>
     <row r="3" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="J3" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>11</v>
@@ -742,7 +702,7 @@
         <v>34</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>33</v>
@@ -769,41 +729,6 @@
         <v>41</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="K5" s="1" t="s">
         <v>11</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4130B519-34FD-4BFF-8ED2-0333BDCCA389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B3CE0AB-6399-42BE-87C2-D80F73E3FCCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,86 +74,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>封开县福利院</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12441225070255594J</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4A626D2D8E918E99A4F23EB867EAE2D0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>收养社会弃婴（儿）和对残疾儿童进行矫正教育，为老年人、残疾人、孤儿和弃婴等特殊群体提供集中居住、生活照料和康复教育的机构。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>封开县江口街道广信四路</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>聂艮华</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>财政补助 （财政补助一类）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>封开县民政局</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2022年02月24日 至 2027年02月23日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>滨州市市政公用发展服务中心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12371600MB23431700</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A1DBA9E5588D9EE45BBE4B3F682FC962</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>贯彻党中央、省关于城镇燃气、城市集中供热、市政设施管理等方面的方针政策和决策部署，落实市委、市政府工作要求。协助做好城镇燃气城市集中供热管理、村镇建设管理、市政公用设施管理、市政公用行业应急管理、市政公用设施养护维修管理、市政公用设施巡查管理等相关工作。负责辖区职责范围内城镇燃气、城市集中供热、市政设施管理等方面工作。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>滨州市黄河五路355号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>徐波</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>待定</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6133.19万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>滨州市住房和城乡建设局</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2026年07月03日 至 2031年03月31日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>郑州大学</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -191,6 +111,86 @@
   </si>
   <si>
     <t>自 2022年06月22日 至 2027年06月22日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>福泉市社会福利院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12522702680170766A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>069238D9848F549506DB2263E5A22ABC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>负责福利院入住人员的管理和服务工作及全市敬老院入住人员的管理和服务工作。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>福泉市磷酸盐厂安置区</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>徐立健</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政补助</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>35万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>福泉市民政局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2026年08月04日 至 2031年08月04日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兴化社会福利院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12321281469272855K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>222737E24DC563C404B545B5F481B406</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提供收养服务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兴化市九顷北路18号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>邹启巧</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全额拨款</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1025万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兴化市民政局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2026年02月03日 至 2029年02月03日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -735,5 +735,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B3CE0AB-6399-42BE-87C2-D80F73E3FCCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35901FE1-6252-49D8-A877-931057ADB0FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>s</t>
   </si>
@@ -74,86 +74,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>郑州大学</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12410000415800376M</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>97E96F7AAB8A38F2E5C26B67DA17A964</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>培养高等学历人才，促进科技文化发展。　哲学类、经济学类、法学类、教育学类、文学类、历史学类、理学类、工学类、农学类、医学类、管理学类大学专科、本科、研究生班、硕士研究生、博士研究生学历教育　博士后培养　相关科学研究、继续教育、专业培训与学术交流　相关社会服务</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>河南省郑州市高新技术开发区科学大道100号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>李蓬</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>财政补助 （财政补助收入、事业收入、其它收入）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>939805万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>河南省教育厅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2022年06月22日 至 2027年06月22日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>福泉市社会福利院</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12522702680170766A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>069238D9848F549506DB2263E5A22ABC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>负责福利院入住人员的管理和服务工作及全市敬老院入住人员的管理和服务工作。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>福泉市磷酸盐厂安置区</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>徐立健</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>财政补助</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>35万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>福泉市民政局</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2026年08月04日 至 2031年08月04日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>兴化社会福利院</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -191,6 +111,46 @@
   </si>
   <si>
     <t>自 2026年02月03日 至 2029年02月03日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>永城市社会福利院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12411481799155635Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4894BFF97FBF775BE1428E7E86796FE3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提供收养服务，弘扬救助精神。 孤儿与弃婴收养 家庭无力照管残疾儿童收养 “三无”老人收养 家庭无力照管老人收养 老人自愿有偿收养 收养对象康复治疗 在华无人照顾海外侨胞与外籍华人收养 相关社会服务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河南省永城市东城区汉润大道77号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李彬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政补助 （财政补助收入）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>28万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>永城市民政局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2023年03月27日 至 2028年03月27日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -576,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -697,41 +657,6 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35901FE1-6252-49D8-A877-931057ADB0FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75B1BA04-4CBD-4A23-A95F-F7AA0CCD9CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="52">
   <si>
     <t>s</t>
   </si>
@@ -151,6 +151,86 @@
   </si>
   <si>
     <t>自 2023年03月27日 至 2028年03月27日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>广西交通职业技术学院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>124500004985067020</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3CD3C2A34FA7B1164022237D3A36B254</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>开展以专科教育为主的高等职业教育，开展职业技能培训、技术服务，培养服务经济社会发展的高素质技术技能人才；开展科学研究、社会服务等工作。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>南宁市兴宁区昆仑大道1258号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李文勇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政补助 （全额拨款）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>44294.996万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>广西壮族自治区交通运输厅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2025年01月03日 至 2030年01月02日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浙江省检验检疫科学技术研究院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1233000073383749XR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AEB94D27CE005E50A7E03435407C1BC1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>为出入境检验检疫提供技术服务。食品和其他农产品、化工、机电、纺织品等商品的检验、检测、检疫、消杀灭和卫生除害及技术开发、转让、培训、咨询服务（涉及资质许可项目需持有资质证书开展）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浙江省杭州市萧山区靖江街道保税路西侧保税物流中心4号库T1区域</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陆勋元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政适当补助 （财政适当补助）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3000万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中华人民共和国杭州海关</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2026年09月08日 至 2027年12月31日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -536,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -657,6 +737,76 @@
         <v>11</v>
       </c>
     </row>
+    <row r="4" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75B1BA04-4CBD-4A23-A95F-F7AA0CCD9CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8EC1761-C4E4-4782-A1FA-743F7ECD2FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="62">
   <si>
     <t>s</t>
   </si>
@@ -231,6 +231,46 @@
   </si>
   <si>
     <t>自 2026年09月08日 至 2027年12月31日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>凯里市鸭塘街道农业农村综合服务中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12522601MB0L572685</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>717DFB3028EB1B1BE3DA6DD28207D561</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>为辖区农业农村事务提供综合服务保障。负责农业农村 乡村振兴 林业 水利技术及技术推广 农业机械化管理 重大动物疫病防控 野生动物保护等具体工作 负责农业种养殖 畜牧兽医 农田水利建设 饮水安全 防汛坑旱 绿化 森林资源保护 森林防火 林业技能推广等具体工作 承担街道党工委 街道办事处交办的其他事项</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>凯里市鸭塘街道月塘大街57号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘学刚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政全额拨款 （财政全额拨款）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.47万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>凯里市人民政府鸭塘街道办事处</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2024年07月31日 至 2029年07月31日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -616,7 +656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -807,6 +847,41 @@
         <v>11</v>
       </c>
     </row>
+    <row r="6" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8EC1761-C4E4-4782-A1FA-743F7ECD2FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{446DF3C3-55B8-423D-A183-3065871D3888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="72">
   <si>
     <t>s</t>
   </si>
@@ -271,6 +271,46 @@
   </si>
   <si>
     <t>自 2024年07月31日 至 2029年07月31日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安徽工程大学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>123400004851217071</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FF961AF72C1EC40DD32B4C34091B8914</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高等专业技术人才学历教育</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>芜湖市鸠江区</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄友锐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政补助 （财政拨款）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>89985万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安徽省教育厅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2025年03月18日 至 2030年03月17日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -656,7 +696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -882,6 +922,41 @@
         <v>11</v>
       </c>
     </row>
+    <row r="7" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{446DF3C3-55B8-423D-A183-3065871D3888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7773A8F0-1C6F-4E48-BF7D-7609B1825689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>s</t>
   </si>
@@ -70,247 +70,47 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>中山大学孙逸仙纪念医院深汕中心医院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3FD1EA80C3F6C207EE2CB95FC49CB7A5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12441500MB2D001104</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>为人民身体健康提供医疗和护理保健服务。 医疗与护理、医学教学、医学研究、卫生医疗人员培训、妇幼保健与健康教育。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>汕尾市城区东涌镇站前横二路1号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陈样新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政补助 （财政核补）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>汕尾市卫生健康局</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2023年08月11日 至 2028年08月10日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>正常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>兴化社会福利院</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12321281469272855K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>222737E24DC563C404B545B5F481B406</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>提供收养服务</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>兴化市九顷北路18号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>邹启巧</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>全额拨款</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1025万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>兴化市民政局</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2026年02月03日 至 2029年02月03日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>永城市社会福利院</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12411481799155635Y</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4894BFF97FBF775BE1428E7E86796FE3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>提供收养服务，弘扬救助精神。 孤儿与弃婴收养 家庭无力照管残疾儿童收养 “三无”老人收养 家庭无力照管老人收养 老人自愿有偿收养 收养对象康复治疗 在华无人照顾海外侨胞与外籍华人收养 相关社会服务</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>河南省永城市东城区汉润大道77号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>李彬</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>财政补助 （财政补助收入）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>28万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>永城市民政局</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2023年03月27日 至 2028年03月27日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>广西交通职业技术学院</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>124500004985067020</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3CD3C2A34FA7B1164022237D3A36B254</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>开展以专科教育为主的高等职业教育，开展职业技能培训、技术服务，培养服务经济社会发展的高素质技术技能人才；开展科学研究、社会服务等工作。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>南宁市兴宁区昆仑大道1258号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>李文勇</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>财政补助 （全额拨款）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>44294.996万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>广西壮族自治区交通运输厅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2025年01月03日 至 2030年01月02日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>浙江省检验检疫科学技术研究院</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1233000073383749XR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AEB94D27CE005E50A7E03435407C1BC1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>为出入境检验检疫提供技术服务。食品和其他农产品、化工、机电、纺织品等商品的检验、检测、检疫、消杀灭和卫生除害及技术开发、转让、培训、咨询服务（涉及资质许可项目需持有资质证书开展）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>浙江省杭州市萧山区靖江街道保税路西侧保税物流中心4号库T1区域</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>陆勋元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>财政适当补助 （财政适当补助）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3000万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中华人民共和国杭州海关</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2026年09月08日 至 2027年12月31日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>凯里市鸭塘街道农业农村综合服务中心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12522601MB0L572685</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>717DFB3028EB1B1BE3DA6DD28207D561</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>为辖区农业农村事务提供综合服务保障。负责农业农村 乡村振兴 林业 水利技术及技术推广 农业机械化管理 重大动物疫病防控 野生动物保护等具体工作 负责农业种养殖 畜牧兽医 农田水利建设 饮水安全 防汛坑旱 绿化 森林资源保护 森林防火 林业技能推广等具体工作 承担街道党工委 街道办事处交办的其他事项</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>凯里市鸭塘街道月塘大街57号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刘学刚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>财政全额拨款 （财政全额拨款）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.47万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>凯里市人民政府鸭塘街道办事处</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2024年07月31日 至 2029年07月31日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>安徽工程大学</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>123400004851217071</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FF961AF72C1EC40DD32B4C34091B8914</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高等专业技术人才学历教育</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>芜湖市鸠江区</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄友锐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>财政补助 （财政拨款）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>89985万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>安徽省教育厅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2025年03月18日 至 2030年03月17日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -696,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -749,212 +549,37 @@
     </row>
     <row r="2" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7773A8F0-1C6F-4E48-BF7D-7609B1825689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD394BA-DC32-4083-80A3-FB6A5758FF10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>s</t>
   </si>
@@ -111,6 +111,46 @@
   </si>
   <si>
     <t>正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>许昌市中心医院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12411000418026291P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>为人民身体健康提供医疗与护理保健服务。 医疗与护理 医学教学与研究 卫生医疗人员培训 卫生技术人员继续教育 保健与健康教育 养老服务 养老业务培训</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河南省许昌市文轩街666号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>张现军</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>非财政补助 （事业收入、经营收入）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>195190.07万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>许昌市卫生健康委员会</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2024年03月06日 至 2027年03月05日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9FEDADEF4F40170FAE85C5F79B7458A2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -496,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -582,6 +622,41 @@
         <v>21</v>
       </c>
     </row>
+    <row r="3" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD394BA-DC32-4083-80A3-FB6A5758FF10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8733655F-2C94-4BFC-AC65-1C5013527539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
   <si>
     <t>s</t>
   </si>
@@ -151,6 +151,46 @@
   </si>
   <si>
     <t>9FEDADEF4F40170FAE85C5F79B7458A2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兰州交通大学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12620000438140606L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B6C78DFDE7CCBCA4FF2ECBCF020BDBDC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>学校依据国家法律法规，全面履行人才培养、科学研究、服务社会、文化传承创新的现代大学职能。办学以本科教育为主体，积极发展研究生和留学生教育，按社会需求办好高等职业教育、成人教育。依法确定学历教育修业年限，实行学分制和弹性学制。依法颁发学业证书和授予学士、硕士及博士学位。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>兰州市安宁区安宁西路118号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聂磊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政补助（全额拨款）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>240296.3万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>甘肃省教育厅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2023年08月29 日 至 2028年08月28日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -536,7 +576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -657,6 +697,41 @@
         <v>21</v>
       </c>
     </row>
+    <row r="4" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8733655F-2C94-4BFC-AC65-1C5013527539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4285CB9-D979-4535-8B80-210F06A6595C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>s</t>
   </si>
@@ -70,90 +70,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>中山大学孙逸仙纪念医院深汕中心医院</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3FD1EA80C3F6C207EE2CB95FC49CB7A5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12441500MB2D001104</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>为人民身体健康提供医疗和护理保健服务。 医疗与护理、医学教学、医学研究、卫生医疗人员培训、妇幼保健与健康教育。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>汕尾市城区东涌镇站前横二路1号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>陈样新</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>财政补助 （财政核补）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10000万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>汕尾市卫生健康局</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2023年08月11日 至 2028年08月10日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>正常</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>许昌市中心医院</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12411000418026291P</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>为人民身体健康提供医疗与护理保健服务。 医疗与护理 医学教学与研究 卫生医疗人员培训 卫生技术人员继续教育 保健与健康教育 养老服务 养老业务培训</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>河南省许昌市文轩街666号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>张现军</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>非财政补助 （事业收入、经营收入）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>195190.07万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>许昌市卫生健康委员会</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2024年03月06日 至 2027年03月05日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9FEDADEF4F40170FAE85C5F79B7458A2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>兰州交通大学</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -191,6 +111,46 @@
   </si>
   <si>
     <t>自 2023年08月29 日 至 2028年08月28日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>江苏省审计厅机关服务中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1232000046600955XG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A9C3BAF86F94B25B9F743413D86D1EDC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>孙夕军</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>为机关办公与职工生活提供后勤服务。 机关办公用房管理服务 机关后勤生活服务 会议接待</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>南京市鼓楼区虎踞关21号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自收自支</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>江苏省审计厅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2023年11月06日 至 2028年11月06日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -576,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -629,42 +589,42 @@
     </row>
     <row r="2" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>11</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>22</v>
@@ -673,63 +633,28 @@
         <v>23</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>26</v>
-      </c>
       <c r="G3" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4285CB9-D979-4535-8B80-210F06A6595C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D06480B0-703B-4770-8167-A4D9E9B40EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
   <si>
     <t>s</t>
   </si>
@@ -151,6 +151,46 @@
   </si>
   <si>
     <t>自 2023年11月06日 至 2028年11月06日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宁波大学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>123300004195291066</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C5D06CC5F2B1CC636F59811AE60CF8CF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>培养高等学历人才，促进科技文化发展。经济、法学等十个学科门类的学历教育及相关继续教育和科学研究</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浙江省宁波市江北区风华路818号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蔡荣根</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政适当补助</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>60684万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浙江省人民政府</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2025年02月27日 至 2030年02月27日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -536,7 +576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -657,6 +697,41 @@
         <v>11</v>
       </c>
     </row>
+    <row r="4" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D06480B0-703B-4770-8167-A4D9E9B40EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04B8850F-009F-445C-9A58-BFA208398BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>s</t>
   </si>
@@ -74,86 +74,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>兰州交通大学</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12620000438140606L</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>B6C78DFDE7CCBCA4FF2ECBCF020BDBDC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>学校依据国家法律法规，全面履行人才培养、科学研究、服务社会、文化传承创新的现代大学职能。办学以本科教育为主体，积极发展研究生和留学生教育，按社会需求办好高等职业教育、成人教育。依法确定学历教育修业年限，实行学分制和弹性学制。依法颁发学业证书和授予学士、硕士及博士学位。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>兰州市安宁区安宁西路118号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>聂磊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>财政补助（全额拨款）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>240296.3万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>甘肃省教育厅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2023年08月29 日 至 2028年08月28日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>江苏省审计厅机关服务中心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1232000046600955XG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A9C3BAF86F94B25B9F743413D86D1EDC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>孙夕军</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>为机关办公与职工生活提供后勤服务。 机关办公用房管理服务 机关后勤生活服务 会议接待</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>南京市鼓楼区虎踞关21号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自收自支</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>200万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>江苏省审计厅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2023年11月06日 至 2028年11月06日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>宁波大学</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -191,6 +111,46 @@
   </si>
   <si>
     <t>自 2025年02月27日 至 2030年02月27日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>运城市广播电视台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12141000012871524P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4B6394EEDB209FE3DD57704835F7BECD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>统筹组织重大宣传报道，组织广播电视创作生产；加快推进媒体深度融合发展，建立全媒体传播体系；拟定广播电视台的发展战略和发展规划；对广播电视台传输覆盖网络统一规划、建设和管理；负责全台广播电视和网络安全播出及设备设施的安全防范工作；组织开展广播电视及新媒体的对外交流与合作。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>运城市盐湖区红旗东街4500号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴宏伟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政拨款</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3337.4万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>运城市人民政府</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2025年03月12日 至 2030年03月11日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -576,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -664,22 +624,22 @@
     </row>
     <row r="3" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>25</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>28</v>
@@ -694,41 +654,6 @@
         <v>31</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K4" s="1" t="s">
         <v>11</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04B8850F-009F-445C-9A58-BFA208398BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D82FE066-996B-4DF6-BE23-78B3E73651E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
   <si>
     <t>s</t>
   </si>
@@ -151,6 +151,46 @@
   </si>
   <si>
     <t>自 2025年03月12日 至 2030年03月11日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沈阳大学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>培养高等学历人才，促进科技文化和教育事业发展；举办大专、本科、硕士研究生、博士研究生学历教育；开展博士后培养、相关科学研究、职业教育、继续教育、专业培训、鉴定咨询、技术研发、技术成果转让与学术交流及相关社会服务等。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沈阳市大东区望花南街21号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵彦志</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全额拨款</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>118676.16万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沈阳市人民政府</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2024年05月29日 至 2029年05月28日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B1D0BD7D7E57833B6F46E54C2C335F98</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">12210100410578227Y	</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -536,7 +576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -624,13 +664,13 @@
     </row>
     <row r="3" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>25</v>
@@ -654,6 +694,41 @@
         <v>31</v>
       </c>
       <c r="K3" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>11</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D82FE066-996B-4DF6-BE23-78B3E73651E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{253073F3-DE06-441E-8A29-18E1E28A7B5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="52">
   <si>
     <t>s</t>
   </si>
@@ -74,86 +74,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>宁波大学</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>123300004195291066</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>C5D06CC5F2B1CC636F59811AE60CF8CF</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>培养高等学历人才，促进科技文化发展。经济、法学等十个学科门类的学历教育及相关继续教育和科学研究</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>浙江省宁波市江北区风华路818号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>蔡荣根</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>财政适当补助</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>60684万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>浙江省人民政府</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2025年02月27日 至 2030年02月27日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>运城市广播电视台</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12141000012871524P</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4B6394EEDB209FE3DD57704835F7BECD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>统筹组织重大宣传报道，组织广播电视创作生产；加快推进媒体深度融合发展，建立全媒体传播体系；拟定广播电视台的发展战略和发展规划；对广播电视台传输覆盖网络统一规划、建设和管理；负责全台广播电视和网络安全播出及设备设施的安全防范工作；组织开展广播电视及新媒体的对外交流与合作。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>运城市盐湖区红旗东街4500号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>吴宏伟</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>财政拨款</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3337.4万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>运城市人民政府</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2025年03月12日 至 2030年03月11日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>沈阳大学</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -191,6 +115,122 @@
   </si>
   <si>
     <t xml:space="preserve">12210100410578227Y	</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>益阳日报社</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12430900446884349R</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新闻采编、报纸印刷、出版、广告刊发。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>益阳市益阳大道（西）209号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>何应超</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政补助（差额）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4001万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中共益阳市委</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2025年12月01日 至 2030年11月30日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0B923EBB16145C48E873CF95C4EAEB9D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>临汾日报社</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12140900113125926C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>负责《临汾日报》及新媒体平台的采访、编辑、出版、发行工作；负责“临汾新闻网”和新媒体平台的管理职责，拓展立体媒体建设。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>山西省临汾市尧都区体育北街41号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘晓军</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3415万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中共临汾市委宣传部</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2025年11月10日 至 2030年11月09日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5DDBD1B790533F3FBBE928D69E3D5137</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>贵州民族报社</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1252000042924602X7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>报道民族新闻和有关信息，促进民族经济发展。 编发民族宗教理论、法律法规、民族宗教知识及文艺副刊等有关稿件 报道民族地区政治经济、科教文卫等各项建设事业取得的新经验、新成就 培训新闻队伍 开展新闻理论、新闻史、应用新闻学等方面的研究及相关广告经营</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>贵阳市南明区箭道街23号贵州民族文化宫10楼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蒙珺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>差额拨款</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>551.91万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>贵州省民族事务委员会</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2025年12月23日 至 2030年12月23日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4970A2421EDA435A4BBF05EC1FDEAF6A</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -576,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -629,34 +669,34 @@
     </row>
     <row r="2" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>21</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>11</v>
@@ -664,13 +704,13 @@
     </row>
     <row r="3" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>23</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>25</v>
@@ -699,36 +739,71 @@
     </row>
     <row r="4" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="K4" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>11</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{253073F3-DE06-441E-8A29-18E1E28A7B5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A1C57A0-7ED0-45DB-9D4C-AE52FB5D7369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -78,86 +78,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>沈阳大学</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>培养高等学历人才，促进科技文化和教育事业发展；举办大专、本科、硕士研究生、博士研究生学历教育；开展博士后培养、相关科学研究、职业教育、继续教育、专业培训、鉴定咨询、技术研发、技术成果转让与学术交流及相关社会服务等。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>沈阳市大东区望花南街21号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>赵彦志</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>全额拨款</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>118676.16万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>沈阳市人民政府</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2024年05月29日 至 2029年05月28日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>B1D0BD7D7E57833B6F46E54C2C335F98</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">12210100410578227Y	</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>益阳日报社</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12430900446884349R</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>新闻采编、报纸印刷、出版、广告刊发。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>益阳市益阳大道（西）209号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>何应超</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>财政补助（差额）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4001万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中共益阳市委</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2025年12月01日 至 2030年11月30日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0B923EBB16145C48E873CF95C4EAEB9D</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>临汾日报社</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -231,6 +151,86 @@
   </si>
   <si>
     <t>4970A2421EDA435A4BBF05EC1FDEAF6A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>湛江市广播电视台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鄂州市融媒体中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12420700MB1B1683X5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>639231DB04631108E5201FF0ED181E54</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宗旨：贯彻落实党中央关于加强和改进党的新闻舆论工作的决策部署，坚持和加强党对新闻舆论工作的集中统一领导。 业务范围：宣传党中央大政方针和省委决策部署，宣传市委市政府中心工作；推动媒体融合，建设新型主流媒体；推进传播能力建设，引导社会舆论，提升正面宣传质量；加强传媒文化产业运营管理。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鄂州市滨湖西路157号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>章丹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政补助</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8646.6万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中共鄂州市委员会</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2025年01月16日 至 2030年01月15日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12440800796299131C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2CD5823C7C5CD49DB89D8901703CF1A0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>开展广播电视宣传，促进广播电视事业和产业发展。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>湛江市赤坎区海滨大道北123号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蔡鸣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>财政核拨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>18.5万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中共湛江市委宣传部</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2026年01月27日 至 2031年01月26日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -675,19 +675,19 @@
         <v>13</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>18</v>
@@ -704,34 +704,34 @@
     </row>
     <row r="3" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="J3" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>11</v>
@@ -739,7 +739,7 @@
     </row>
     <row r="4" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>33</v>
@@ -748,25 +748,25 @@
         <v>34</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>11</v>
@@ -774,34 +774,34 @@
     </row>
     <row r="5" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>43</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>11</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A1C57A0-7ED0-45DB-9D4C-AE52FB5D7369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7046D2B-E743-48B7-84DD-8DFA07FA36E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
   <si>
     <t>s</t>
   </si>
@@ -74,86 +74,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>财政拨款</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>临汾日报社</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12140900113125926C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>负责《临汾日报》及新媒体平台的采访、编辑、出版、发行工作；负责“临汾新闻网”和新媒体平台的管理职责，拓展立体媒体建设。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>山西省临汾市尧都区体育北街41号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刘晓军</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3415万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中共临汾市委宣传部</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2025年11月10日 至 2030年11月09日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5DDBD1B790533F3FBBE928D69E3D5137</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>贵州民族报社</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1252000042924602X7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>报道民族新闻和有关信息，促进民族经济发展。 编发民族宗教理论、法律法规、民族宗教知识及文艺副刊等有关稿件 报道民族地区政治经济、科教文卫等各项建设事业取得的新经验、新成就 培训新闻队伍 开展新闻理论、新闻史、应用新闻学等方面的研究及相关广告经营</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>贵阳市南明区箭道街23号贵州民族文化宫10楼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>蒙珺</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>差额拨款</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>551.91万元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>贵州省民族事务委员会</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自 2025年12月23日 至 2030年12月23日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4970A2421EDA435A4BBF05EC1FDEAF6A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>湛江市广播电视台</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -231,6 +151,42 @@
   </si>
   <si>
     <t>自 2026年01月27日 至 2031年01月26日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鄂尔多斯应用技术学院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12152700MB11816672</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AD58E9693EF3F56591DD7CC6E6C4C6ED</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>牢牢把握铸牢中华民族共同体意识工作主线，将之贯穿于办学治校、教书育人及自身建设等全过程、各方面。培养区域经济社会发展所需要的应用型技术技能型人才。承担机械工程 土木工程 自动化 交通运输 化学工程与工艺等专业以本科教育为主的学历教育。开展继续教育 专业进修培训 学术交流 科学研究及相关社会服务。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内蒙古鄂尔多斯市康巴什区鄂尔多斯大街东1号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宫箭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>159797万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鄂尔多斯市人民政府</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2024年04月16日 至 2029年04月15日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -616,7 +572,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -669,7 +625,7 @@
     </row>
     <row r="2" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>13</v>
@@ -678,25 +634,25 @@
         <v>14</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>11</v>
@@ -704,34 +660,34 @@
     </row>
     <row r="3" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>11</v>
@@ -739,71 +695,36 @@
     </row>
     <row r="4" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="J4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="K4" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="K5" s="1" t="s">
         <v>11</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面文件\sydwCx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7046D2B-E743-48B7-84DD-8DFA07FA36E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A1871CE-5E7B-4F08-B307-B4C7373609D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
   <si>
     <t>s</t>
   </si>
@@ -187,6 +187,46 @@
   </si>
   <si>
     <t>自 2024年04月16日 至 2029年04月15日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>榆林大学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>126100004366899378</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DA1E7F749413FDD06EF924BC8868292E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>培养高等本科学历、研究生学历人才，促进科技文化发展。工学类、农学类、理学类、文学类、教育学类学科高等本科学历、研究生学历教育；相关科学研究；继续教育；专业培训；学术交流。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陕西省榆林市文化北路2号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>付峰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全额拨款</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>68826万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陕西省教育厅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自 2026年04月14日 至 2031年04月14日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -572,7 +612,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultColWidth="18.9296875" defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.9296875" style="1"/>
@@ -728,6 +768,41 @@
         <v>11</v>
       </c>
     </row>
+    <row r="5" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
